--- a/public/expense_template.xlsx
+++ b/public/expense_template.xlsx
@@ -16,8 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy/m/d"/>
+    <numFmt numFmtId="165" formatCode="#,##0"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -818,10 +819,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" applyNumberFormat="1" fontId="1" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" applyNumberFormat="1" fontId="1" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -887,7 +888,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" applyNumberFormat="1" fontId="1" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
